--- a/docs/security/CKAM_ISO27001_CONTROL_MATRIX.xlsx
+++ b/docs/security/CKAM_ISO27001_CONTROL_MATRIX.xlsx
@@ -10,7 +10,7 @@
     <sheet name="ISO27001 Annex A" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISO27001 Annex A'!$A$1:$M$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ISO27001 Annex A'!$A$1:$P$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,22 +430,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="48" customWidth="1" min="6" max="6"/>
     <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="48" customWidth="1" min="11" max="11"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
     <col width="48" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="48" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,57 +464,72 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Control Kind</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Applicable</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Existing Evidence</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Technical Control</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Process Control Needed</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Control Owner</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Gap</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Risk</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Recommended Action</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Evidence Needed</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Draft Policy (DRAFT - not evidence)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Previous Status (2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -528,55 +546,70 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>Policies for information security</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md; docs/ai/DEVELOPMENT_GUARDRAILS.md (engineering rules only); docs/security/CKAM_SECURITY_BASELINE.md (draft 2026-10-15)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>CLAUDE.md; docs/ai/DEVELOPMENT_GUARDRAILS.md (engineering rules only); docs/security/CKAM_SECURITY_BASELINE.md (draft 2026-10-15); docs/security/policies/01_Information_Security_Policy.md and 14 further drafts (2026-10-16; DRAFT - MANAGEMENT APPROVAL REQUIRED; 0 approved, 0 operating; not evidence of operation)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>NO TECH COMPONENT: policies are management documents</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Management-approved information security policy plus topic policies (access control, backup, cryptography, change, incident, supplier, acceptable use, privacy); annual review</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Management (CKAM owner) with ISMS lead (to appoint)</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>No approved ISMS policy set exists; only engineering guardrails</t>
-        </is>
-      </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>Policy set exists only as DRAFT (15 documents, 0 approved, 0 communicated, 0 records); only the engineering guardrails operate</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>R-24 (High), R-31 (Medium)</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Draft and approve the policy set (EXT-17)</t>
-        </is>
-      </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>Approve the draft pack (decision SD-16, EXT-17), communicate it, collect acknowledgements</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>Signed policy documents, version history, proof of communication to staff</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -595,55 +628,70 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>Information security roles and responsibilities</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md (owner approves every push and every deploy); docs/ai/CKAM_PRODUCTION_SERVER_CHECKLIST.md (backup, restore and rollback owners listed as Not yet assigned)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>CLAUDE.md (owner approves every push and every deploy); docs/ai/CKAM_PRODUCTION_SERVER_CHECKLIST.md (backup, restore and rollback owners listed as Not yet assigned); docs/security/policies/01_Information_Security_Policy.md roles section (DRAFT)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>NO TECH COMPONENT: application roles exist (Head-office Admin, Full Admin, Can Add &amp; Move Assets, View Only, Own Assets Only) but these are user roles, not ISMS roles</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Name an ISMS lead, CKAM system owner, backup owner, restore owner, deploy operator, incident coordinator; record in a RACI</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Management</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Only push/deploy approval is defined; operational security roles are unassigned</t>
-        </is>
-      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
+          <t>Roles are described in a DRAFT only; no one is appointed; operational security roles unassigned</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
           <t>R-24 (High)</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Approve a CKAM RACI (EXT-17, EXT-36)</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Signed RACI, appointment notes</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -662,55 +710,70 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>Segregation of duties</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>backend/app/core/capabilities.py; docs/ai/DECISIONS.md 2026-10-14 entries (3),(5),(8); docs/security/evidence/access/tests.csv (17 escalation cases, 0 failures)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>backend/app/core/capabilities.py; docs/ai/DECISIONS.md 2026-10-14 entries (3),(5),(8); docs/security/evidence/access/tests.csv (17 escalation cases, 0 failures); docs/security/evidence/closure/retest2/access/RETEST2_ACCESS.md (217 routes x 14 identities = 3,038 cells, 0 escalations)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>TECH READY: head-office-only actions (code rules, companies, custom fields, ERP Inbox), a Full Admin cannot reset a head-office admin password, a PO with received assets can never be deleted</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Separate the person who develops from the person who approves production change; separate DB owner from runtime account; second reviewer for code</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Management; Dev lead</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>One person writes code, commits and (with owner approval) deploys; no independent code review (IF-17)</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>R-23 (High), R-24 (High)</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Introduce a second reviewer or approver for production changes; role split (EXT-07, EXT-35)</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Change records showing a different approver; DB role list</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02, 04</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -729,55 +792,70 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>Management responsibilities</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Management requires staff and suppliers to apply security policies; budget and resources for ISMS</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Management</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>No evidence of management direction on information security</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>R-24 (High)</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Management commitment statement and resourcing decision (EXT-36)</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Minutes of management review, signed commitment</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01, 14</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -796,55 +874,70 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>Contact with authorities</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Maintain contacts for CERT-In (Indian cyber-incident reporting; confirm the reporting window with legal counsel), police cyber cell, data-protection authority when applicable</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Management; Legal</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>No authority contact list or reporting procedure</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>R-31 (Medium)</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Add to the incident response plan (EXT-20, EXT-31)</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Contact list, reporting procedure</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -863,55 +956,70 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>Contact with special interest groups</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Subscribe to advisories for Python, FastAPI, PostgreSQL, Windows Server, NAS vendor</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>No subscriptions evidenced</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>R-15 (Medium), R-17 (High)</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Subscribe the IT mailbox to vendor security advisories</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Subscription list</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 06</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -930,55 +1038,70 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>Threat intelligence</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/infra/dependency_audit.md; docs/security/evidence/infra/raw/pip_audit.json; docs/security/evidence/infra/raw/npm_audit_prod.json (one-off run 2026-10-15)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>docs/security/evidence/infra/dependency_audit.md; docs/security/evidence/infra/raw/pip_audit.json; docs/security/evidence/infra/raw/npm_audit_prod.json (one-off run 2026-10-15); docs/security/evidence/closure/backend/dependency_recheck.md; docs/security/evidence/closure/infra/npm_audit_recheck.md; docs/security/evidence/closure/retest2/infra/raw/pip_audit_constraints.txt (re-runs 2026-10-16); docs/security/policies/06_Vulnerability_Management_Procedure.md (DRAFT)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: advisory scans can be run (npm audit, pip-audit) but are not scheduled</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Monthly review of advisories relevant to the CKAM stack; record decisions</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Dev lead; IT/Infra</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Only a one-off scan exists; no ongoing threat-intelligence process</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>Only one-off scans (2026-10-15/16); the monthly advisory review exists only in DRAFT doc 06 and has never run</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>R-15 (Medium)</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Schedule monthly dependency and advisory review (EXT-09, EXT-12)</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Monthly scan reports with decisions</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 06</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -997,55 +1120,70 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>Information security in project management</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/CKAM_SIMPLIFICATION_S0_REPORT.md (security fixes before redesign); docs/ai/AM-09_RC_FULL_AUDIT_REPORT.md; docs/ai/DECISIONS.md 2026-10-14 (1) guardrails; this VAPT evidence set</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/CKAM_SIMPLIFICATION_S0_REPORT.md (security fixes before redesign); docs/ai/AM-09_RC_FULL_AUDIT_REPORT.md; docs/ai/DECISIONS.md 2026-10-14 (1) guardrails; this VAPT evidence set; docs/security/CKAM_SECURITY_CLOSURE_REGISTER.md; docs/security/CKAM_SECURITY_DECISIONS_REQUIRED.md (closure programme 2026-10-16)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: security tests are part of each stage's test run</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Add a security checklist to every stage plan (use CKAM_SECURITY_BASELINE.md)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Security is applied by practice, not by a mandatory project step</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Make the baseline checklist mandatory in each stage report</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Completed checklist per stage</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04, 12</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1064,55 +1202,70 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>Inventory of information and other associated assets</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (servers, folders, DB, NAS, task, firewall rule); docs/ai/ERP_INTEGRATION.md; docs/security/evidence/infra/raw/pip_freeze_image.txt; frontend/package-lock.json</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: CKAM itself is CityKart's physical asset register (custody, status, holder); system components are documented</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Information-asset register for CKAM (data sets, servers, secrets, backups) with owner and classification</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>ISMS lead; IT/Infra</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>No formal information-asset register with owners and classification</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>R-11 (Medium)</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Create the register from PRODUCTION_INFRASTRUCTURE.md and the threat model data stores</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Approved asset register</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01, 12</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1131,55 +1284,70 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Acceptable use of information and other associated assets</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Acceptable-use rules for CKAM users (no shared passwords, store login use, export handling)</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>HR; Management</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>No acceptable-use policy evidenced</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>R-30 (Medium), R-11 (Medium)</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Publish acceptable-use rules (EXT-17)</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Signed acknowledgements</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01, 10</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -1198,55 +1366,70 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Return of assets</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/DECISIONS.md 2026-10-14 (9) (a person or place that still holds assets cannot be deactivated); Move screen Return to Stock Room (docs/ai/DECISIONS.md (10))</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>TECH READY: CKAM records who holds each asset and blocks deactivation of a person who still holds assets</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>HR leaver checklist that uses CKAM's list of assets held by the leaver</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>HR; IT</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Leaver process linking HR and CKAM not evidenced</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>R-09 (Medium)</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Define leaver step: return all CKAM assets before final settlement (EXT-33)</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Leaver checklist records</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 03</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1265,55 +1448,70 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Classification of information</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED (de facto: logs are head-office-admin only, docs/ai/LOGGING_AND_DIAGNOSTICS.md section 9)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: access restrictions exist per role but no classification scheme drives them</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Classification scheme (e.g. Public, Internal, Confidential, Restricted) applied to CKAM data sets</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>ISMS lead</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>No classification scheme</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>R-11 (Medium)</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>Classify CKAM data sets (vendor commercial data, invoices, staff PII, audit logs, secrets)</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Classification register</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1332,55 +1530,70 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Labelling of information</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>TECH MISSING: exports (xlsx/csv) carry no classification marking</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Label confidential exports and reports</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Dev lead; ISMS lead</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Exports are unlabelled</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>R-11 (Medium)</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Add a confidentiality footer or sheet header to exports once classification is approved</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Sample labelled export</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1399,55 +1612,70 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Information transfer</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>docs/security/evidence/input/formula_export_cell.txt; docs/ai/LOGGING_AND_DIAGNOSTICS.md (EXPORT audit rows); docs/ai/PRODUCTION_INFRASTRUCTURE.md (plain HTTP)</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: every export is audited and formula-injection safe; temporary passwords are shown once; but all traffic is plain HTTP (IF-02)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Rules for sending exports and temporary passwords (out-of-band, not email/chat)</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>IT; ISMS lead</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Transfer over the internet is unencrypted; no transfer rules</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>R-01 (High), R-11 (Medium)</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>HTTPS (EXT-04); transfer rules in policy (EXT-17)</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>HTTPS test result; policy</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1466,55 +1694,70 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Access control</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/access/authz_matrix.csv (217 routes x 11 personas, zero escalation, also in the final retest); docs/security/evidence/access/tests.csv; backend/app/core/capabilities.py; backend/app/core/deps.py; docs/security/CKAM_SECURITY_REMEDIATION_REPORT.md (AC-1, AC-2, IF-03 FIXED: commits 77431ba, 7e57844)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>TECH READY: backend authorization is authoritative; zero privilege escalation; company, work-area and own-custody scoping; AC-1, AC-2, IF-03 fixed and retested (local commits, not yet deployed)</t>
+          <t>docs/security/evidence/access/authz_matrix.csv (217 routes x 11 personas, zero escalation, also in the final retest); docs/security/evidence/access/tests.csv; backend/app/core/capabilities.py; backend/app/core/deps.py; docs/security/CKAM_SECURITY_REMEDIATION_REPORT.md (AC-1, AC-2, IF-03 FIXED: commits 77431ba, 7e57844); docs/security/evidence/closure/retest2/access/authz_matrix.csv (second retest on the final code: 217 routes x 14 identities = 3,038 cells, 0 escalations); docs/security/policies/02_Access_Control_Policy.md (DRAFT)</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>TECH READY: backend authorization is authoritative; zero privilege escalation; company, work-area and own-custody scoping; AC-1, AC-2, IF-03 fixed and retested (local commits, not yet deployed); Retested again in the closure stage (retest 1 and retest 2, 0 escalations); still local commits, not deployed</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>Written access-control policy; owner decision D6 (should a Full Admin be limited to chosen companies)</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>Management; Dev lead</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>No written access-control policy; D6 open; fixes not yet in production</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>Access-control policy is DRAFT only; D6 open; AC-1, AC-2, IF-03 fixes not deployed (production 3b5e842)</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>R-04 (High), R-10 (Medium)</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Approve policy; decide D6 (EXT-26); deploy (EXT-01)</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Policy; deploy record</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1533,55 +1776,70 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Identity management</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>docs/security/evidence/infra/db_02_triggers_constraints.out.txt (unique company+code and company+email); docs/ai/DECISIONS.md 2026-10-14 (9) store logins sm.&lt;code&gt;@citykartstores.com</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: one record per person, deactivate not delete, login can be switched off; but each store has one login likely used by several staff</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Joiner/mover/leaver procedure; rule on shared store logins</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>HR; IT</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>No JML procedure; store logins are shared identities</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>R-30 (Medium), R-16 (Medium)</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>JML process (EXT-33); store-login policy (EXT-30)</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>JML records; store-login register</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02, 03</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1600,55 +1858,70 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Authentication information</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>docs/security/evidence/auth/tests.csv AU-T044..AU-T050 (Argon2id, temporary password shown once, must change at first sign-in)</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>TECH PARTIAL: Argon2id hashing, no plaintext anywhere; password policy enforced in code (AU-08 FIXED: backend/app/auth/password_policy.py, common words with numbers refused); but passwords cross the internet in plain HTTP (IF-02)</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: Argon2id hashing, no plaintext anywhere; password policy enforced in code (AU-08 FIXED: backend/app/auth/password_policy.py, common words with numbers refused); but passwords cross the internet in plain HTTP (IF-02); refresh tokens are tracked server-side only as a SHA-256 hash of the token id (auth_session, AU-06 FIXED in code, not deployed); stricter name look-alike passwords (7b039fb)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>Written password policy; secure hand-over of temporary passwords; password manager for server secrets</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>IT; Dev lead</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Plaintext transport; server secrets handling not formalised; new policy not yet deployed</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>R-05 (High), R-01 (High), R-03 (Critical)</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>HTTPS (EXT-04); password manager (EXT-23); deploy (EXT-01)</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Policy; config showing rules; vault inventory</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1667,55 +1940,70 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Access rights</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md (ACCESS_CHANGED, PRIMARY_OWNER_GRANTED/_REVOKED rows); GET /api/asset-users/export (docs/security/evidence/access/authz_matrix.csv)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md (ACCESS_CHANGED, PRIMARY_OWNER_GRANTED/_REVOKED rows); GET /api/asset-users/export (docs/security/evidence/access/authz_matrix.csv); docs/security/policies/11_Periodic_Access_Review_Procedure.md and templates/access_review_record.md (DRAFT, never run)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: every access change is audited and the user list can be exported</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Quarterly access review with sign-off; approval record for every grant</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>CKAM owner (head-office admin)</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>No periodic access review; grants have no request/approval record</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>R-04 (High), R-16 (Medium)</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Quarterly access review (EXT-18)</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>Signed review of exported user list</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02, 03, 11</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1734,55 +2022,70 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Information security in supplier relationships</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>NOT EVIDENCED (suppliers in scope: ERP warehouse team, NAS, GitHub, AI coding assistant provider, Google Fonts, Python/npm ecosystems)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>NOT EVIDENCED (suppliers in scope: ERP warehouse team, NAS, GitHub, AI coding assistant provider, Google Fonts, Python/npm ecosystems); docs/security/policies/09_Supplier_Security_Review.md (DRAFT); Google Fonts drops out of the supplier list once the self-hosted fonts (79dbae7) are deployed</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Supplier security policy and supplier list with risk rating</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Management; IT</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>No supplier security process</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>No operating supplier security process (DRAFT doc 09 only)</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>R-26 (Medium), R-08 (Medium)</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Supplier review (EXT-34)</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>Supplier register with assessment</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 09</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -1801,55 +2104,70 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Addressing information security within supplier agreements</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Security clauses in agreements (NAS/hardware support, any external developer or auditor)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Management; Legal</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>No agreements evidenced</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>R-26 (Medium)</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Review agreements (EXT-34)</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Agreements with security clauses</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 09</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -1868,55 +2186,70 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Managing information security in the ICT supply chain</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>frontend/package-lock.json; docs/security/evidence/infra/raw/npm_audit_prod.json (0 production vulnerabilities); docs/security/evidence/infra/dependency_audit.md; backend/pyproject.toml; backend/constraints.txt (IF-11 FIXED: file added in ae706bb)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: npm is locked; Python constraints file exists but the production install does not use it yet; python-jose/ecdsa advisories not reachable (IF-12 ACCEPTED)</t>
+          <t>frontend/package-lock.json; docs/security/evidence/infra/raw/npm_audit_prod.json (0 production vulnerabilities); docs/security/evidence/infra/dependency_audit.md; backend/pyproject.toml; backend/constraints.txt (IF-11 FIXED: file added in ae706bb); docs/security/evidence/closure/backend/dependency_recheck.md; docs/security/evidence/closure/retest2/infra/raw/pip_audit_constraints.txt; ops/windows/deploy_ckam.ps1.template (installs with -c constraints.txt; reference only)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: npm is locked; Python constraints file exists but the production install does not use it yet; python-jose/ecdsa advisories not reachable (IF-12 ACCEPTED); pip-audit on constraints.txt re-run in the closure stage: python-jose and ecdsa have no fixed version, not reachable (HS256 pinned, no asymmetric keys), ACCEPTED; PyJWT replacement recommended (EXT-47); npm --omit=dev 0 vulnerabilities, one dev-only HIGH in a build tool (OBS-NPM-DEV)</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>Dependency approval before adding/upgrading (now in DEVELOPMENT_GUARDRAILS.md); constrained installs in production</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>Production deploy not yet wired to constraints.txt</t>
-        </is>
-      </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>Production deploy not yet wired to constraints.txt (the reference deploy script is, but has never run on 10.0.1.98: EXT-12, EXT-13); PyJWT migration open</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>R-15 (Medium)</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Constraints/lock file and use it in deploy (EXT-12)</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Lock file in git; deploy log showing constrained install</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 06, 09</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -1935,55 +2268,70 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Monitoring, review and change management of supplier services</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/ERP_INTEGRATION.md (sync_success / sync_failed system events; ERP data as of); docs/ai/LOGGING_AND_DIAGNOSTICS.md (diagnostics/health minutes since last ERP copy)</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: ERP copy freshness and failures are recorded</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Periodic review of ERP feed, NAS and other supplier services; notice of supplier changes (e.g. ERP view grants lost on rebuild)</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>IT; ERP warehouse owner</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>No scheduled review; grant-loss risk documented but not monitored</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>R-08 (Medium)</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Weekly check of ERP sync events (EXT-22)</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Review log</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 09</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2002,55 +2350,70 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Information security for use of cloud services</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>git remote origin = GitHub (repository under a personal GitHub account); frontend/index.html loads Google Fonts; commits co-authored by an AI coding assistant</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>git remote origin = GitHub (repository under a personal GitHub account); frontend/index.html loads Google Fonts; commits co-authored by an AI coding assistant; Fonts self-hosted in code (frontend/src/fonts.css, 79dbae7; CSP without Google hosts, b401e9f), not deployed: production 3b5e842 still loads Google Fonts</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Cloud-use policy: which cloud services may hold CKAM code or data; account ownership and MFA</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Management; Dev lead</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Repository ownership, visibility and MFA not evidenced; no cloud-use rules</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>R-26 (Medium), R-29 (Low)</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Move repository to a company-owned organisation with MFA (EXT-28); self-host fonts (EXT-11)</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Repository settings screenshot; policy</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 09</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -2069,55 +2432,70 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Information security incident management planning and preparation</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md section 1 (request id support workflow) and section 10 (playbook); frontend/src/features/support/report-problem-store.ts</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md section 1 (request id support workflow) and section 10 (playbook); frontend/src/features/support/report-problem-store.ts; docs/security/policies/05_Incident_Response_Plan.md and templates/incident_record.md (DRAFT); docs/security/CKAM_URGENT_PRODUCTION_SECURITY_RUNBOOK.md (prepared, not executed)</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: request ids, Report a problem, logs by request, diagnostics bundle</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Incident response plan: roles, severity, containment, communication, CERT-In reporting, evidence handling</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>ISMS lead; IT</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>No incident response plan</t>
-        </is>
-      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>Incident response plan exists only as DRAFT; never approved or exercised</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>R-27 (High), R-02 (Critical)</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Write and test the plan (EXT-20)</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Approved plan, tabletop exercise record</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2136,55 +2514,70 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Assessment and decision on information security events</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md (error grouping by fingerprint; SECURITY rows)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md (error grouping by fingerprint; SECURITY rows); docs/security/policies/05_Incident_Response_Plan.md severity table (DRAFT)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: events are recorded and grouped</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Triage criteria for when an event becomes an incident</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>ISMS lead</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>No triage criteria</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>Triage criteria exist only as DRAFT; no triage record</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>R-27 (High)</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Include triage table in IR plan (EXT-20)</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Triage records</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2203,55 +2596,70 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Response to information security incidents</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>NOT EVIDENCED (IF-01 response: fix in commit 3e134c1, retested; production deploy and secret rotation still pending)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>NOT EVIDENCED (IF-01 response: fix in commit 3e134c1, retested; production deploy and secret rotation still pending); docs/security/CKAM_URGENT_PRODUCTION_SECURITY_RUNBOOK.md (deploy, rotation and compromise-assessment phases prepared, NOT executed); docs/security/policies/05_Incident_Response_Plan.md (DRAFT)</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Documented response steps; IF-01 handled as an incident (contain, rotate, assess, record)</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>ISMS lead; IT</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>No documented response; IF-01 production exposure not yet contained</t>
-        </is>
-      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>IF-01 production exposure not contained (nothing deployed, no secret rotated, no compromise assessment, no incident record)</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
           <t>R-02 (Critical), R-03 (Critical)</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Treat IF-01 as an incident now (EXT-01, EXT-02, EXT-03)</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Incident record for IF-01</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2270,55 +2678,70 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Learning from information security incidents</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/REVIEW_FINDINGS.md; docs/ai/RC_ISSUES.md; docs/security/evidence/ (findings with regression tests)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/REVIEW_FINDINGS.md; docs/ai/RC_ISSUES.md; docs/security/evidence/ (findings with regression tests); docs/security/CKAM_SECURITY_CLOSURE_REGISTER.md; docs/security/CKAM_SECURITY_BASELINE.md (closure lessons added 2026-10-16)</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: each security fix carries a regression test</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Post-incident review template; lessons fed into the baseline</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>ISMS lead; Dev lead</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Lessons captured informally</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Post-incident review for IF-01; add lesson to baseline (file-serving review rule)</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Review record</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2337,55 +2760,70 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Collection of evidence</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md (audit_log append-only, request id, actor, IP; export as jsonl); docs/security/evidence/infra/db_03_append_only_privilege_tests.out.txt</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>TECH PARTIAL: append-only audit with export; TRUNCATE guards and 5-year purge floor added (IF-05/IF-06 MITIGATED, migration a3c5e7f9b1d4); the DB owner or superuser can still drop triggers and logs stay on the same server</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: append-only audit with export; TRUNCATE guards and 5-year purge floor added (IF-05/IF-06 MITIGATED, migration a3c5e7f9b1d4); the DB owner or superuser can still drop triggers and logs stay on the same server; owner/migrator/runtime role split proven on a disposable DB (ops/db, 734fd19) but not applied in production; EXT-41 (preserve logs before the IF-01 deploy) prepared, not done</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>Evidence handling procedure (export, hash, store off-server, chain of custody)</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>ISMS lead; IT</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Evidence integrity not protected against the DB owner; no off-server copy</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>R-12 (Medium)</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Role split (EXT-07); off-server log shipping (EXT-21)</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Procedure; hashed export samples</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2404,55 +2842,70 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Information security during disruption</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>NOT EVIDENCED</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
+          <t>NOT EVIDENCED; docs/security/policies/08_Business_Continuity_and_DR_Plan.md (DRAFT)</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Keep security controls active during an outage or restore (no temporary open access)</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>ISMS lead; IT</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>Not addressed</t>
-        </is>
-      </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
+          <t>Addressed only in a DRAFT plan; not approved or tested</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
           <t>R-13 (High)</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Include in BCP/DR plan (EXT-29)</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>BCP section</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2471,55 +2924,70 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>ICT readiness for business continuity</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (daily dump 03:00, 30 days; previous releases kept for rollback; scheduled task restarts every minute)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (daily dump 03:00, 30 days; previous releases kept for rollback; scheduled task restarts every minute); docs/security/CKAM_BACKUP_RESTORE_PLAN.md (prepared); docs/security/policies/07_Backup_Restore_Policy.md and 08 (DRAFT)</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: daily backup and code rollback exist; no off-server copy, no production restore test, no RTO/RPO agreed (IF-08)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>BCP/DR plan with RTO/RPO, reboot test, restore drill</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>IT/Infra; Management</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>No agreed recovery objectives; never restored in production</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>R-13 (High), R-14 (High)</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>EXT-08, EXT-29</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Restore drill report with timings</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2538,55 +3006,70 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Legal, statutory, regulatory and contractual requirements</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Register of applicable law (Digital Personal Data Protection Act 2023, IT Act 2000 and CERT-In directions, record-keeping for fixed-asset and tax records)</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Legal; Management</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>No legal register</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>R-31 (Medium)</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Legal review (EXT-31)</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Legal register</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01, 12</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -2605,55 +3088,70 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Intellectual property rights</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>frontend/package-lock.json and docs/security/evidence/infra/raw/pip_freeze_image.txt list components; licences not reviewed</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Open-source licence review; font licence (self-hosting Google Fonts must respect their licence)</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Licences not reviewed</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>R-15 (Medium)</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>Run a licence report once a year</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Licence report</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 06, 09</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -2672,55 +3170,70 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>Protection of records</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/infra/db_02_triggers_constraints.out.txt (9 append-only / identity triggers); docs/security/evidence/auth/tests.csv AU-T091..AU-T093; CLAUDE.md rule 2 (no hard deletes)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: asset_event, asset_field_change, audit_log, master_audit guarded against UPDATE, DELETE and TRUNCATE; audit purge refused for rows younger than 5 years; asset_code immutable; no hard deletes; owner/superuser can still drop triggers (IF-05/IF-06 MITIGATED)</t>
+          <t>docs/security/evidence/infra/db_02_triggers_constraints.out.txt (9 append-only / identity triggers); docs/security/evidence/auth/tests.csv AU-T091..AU-T093; CLAUDE.md rule 2 (no hard deletes); migration backend/app/alembic/versions/c6e8a0b2d4f6_asset_lifecycle_fields_guard.py; backend/tests/lifecycle/test_obs_status_guard.py; docs/security/evidence/closure/db/WPB_RESULTS.md</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: asset_event, asset_field_change, audit_log, master_audit guarded against UPDATE, DELETE and TRUNCATE; audit purge refused for rows younger than 5 years; asset_code immutable; no hard deletes; owner/superuser can still drop triggers (IF-05/IF-06 MITIGATED); closure: a DB trigger refuses changes to asset.status / current_asset_user_id / status_since unless the transaction carries the apply_events marker (c6e8a0b2d4f6; marker settable by anyone with SQL as the app role, so defence in depth only); role split scripts proven locally; none of it deployed</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
           <t>Retention schedule for business records; archiving procedure for audit_log</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Management; DBA</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Owner/superuser can still destroy records; backups not off-server</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>R-12 (Medium), R-13 (High)</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>EXT-07, EXT-08; retention schedule (EXT-21)</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Role list showing split; retention schedule</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 07</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2739,55 +3252,70 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Privacy and protection of personal identifiable information (PII)</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md section 3 (redaction) and section 9 (privacy notes); backend/app/observability/redact.py; docs/security/evidence/auth/tests.csv AU-T049</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>TECH PARTIAL: secrets redacted; logs admin-only; staff PII (name, code, email, phone), vendor contacts and IP addresses are stored; audit_log kept forever</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: secrets redacted; logs admin-only; staff PII (name, code, email, phone), vendor contacts and IP addresses are stored; audit_log kept forever; self-hosted fonts stop sending staff IP addresses to Google once deployed (79dbae7)</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t>Privacy notice to staff, lawful basis, retention, handling of correction/erasure requests within append-only design</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Legal; Management; Dev lead</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>No privacy notice or PII retention rule</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
         <is>
           <t>R-11 (Medium), R-31 (Medium)</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>EXT-31; decide PII retention vs append-only</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Privacy notice; retention decision</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2806,55 +3334,70 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>Independent review of information security</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/ (internal VAPT 2026-10-15 by the engineering team, not independent)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t>docs/security/evidence/ (internal VAPT 2026-10-15 by the engineering team, not independent); Closure retests 1 and 2 (docs/security/evidence/closure/retest1, retest2) were run by testers separate from the fixers but inside the same engineering programme: not independent in the ISO sense</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Independent review at planned intervals (external VAPT, internal audit by someone independent of development)</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Management</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>No independent review</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>External VAPT (EXT-14); internal audit (EXT-36)</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Independent report</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 13</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -2873,55 +3416,70 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>Compliance with policies, rules and standards for information security</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>backend/tests/observability/test_coverage_walker.py (fails on any unclassified write route); backend/tests/conftest.py (refuses tests on the plain ckam DB); docs/ai/DEVELOPMENT_GUARDRAILS.md security rules</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
+          <t>backend/tests/observability/test_coverage_walker.py (fails on any unclassified write route); backend/tests/conftest.py (refuses tests on the plain ckam DB); docs/ai/DEVELOPMENT_GUARDRAILS.md security rules; backend/tests/security/test_least_privilege_role_split.py; frontend/scripts/check-build-security.mjs; frontend/scripts/check-nginx-live.mjs; frontend/src/security/nginx-config.test.ts; ops/db/check_least_privilege.sql</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: some rules are enforced by tests; security rules written into the guardrails</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Periodic compliance check against the baseline and policies</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>ISMS lead</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Policies to comply with do not exist yet</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>After EXT-17, add quarterly compliance check</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Compliance checklist results</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 13</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -2940,55 +3498,70 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>Documented operating procedures</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md; docs/ai/LOGGING_AND_DIAGNOSTICS.md; docs/ai/CKAM_RELEASE_RUNBOOK.md (describes Docker; production is Windows without Docker: IF-15)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: procedures exist but the production launcher and release script are not in git</t>
+          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md; docs/ai/LOGGING_AND_DIAGNOSTICS.md; docs/ai/CKAM_RELEASE_RUNBOOK.md (describes Docker; production is Windows without Docker: IF-15); ops/windows/README.md and secret-free templates run_ckam_web.ps1.template, deploy_ckam.ps1.template, rollback_release.ps1.template, verify_release.ps1 (parser + -WhatIf validated); docs/security/CKAM_URGENT_PRODUCTION_SECURITY_RUNBOOK.md; ops/db/ROLE_SPLIT_RUNBOOK.md (all prepared, none executed on production)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: procedures exist but the production launcher and release script are not in git; closure: reference Windows launcher/deploy/verify/rollback scripts are in git (IF-15 code/reference side); the LIVE launcher is still not in git (EXT-13)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>Current, version-controlled production runbook (deploy, restore, rotate secrets, reboot)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>IT/Infra; Dev lead</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Runbook does not match production; scripts outside git</t>
-        </is>
-      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>Live launcher not in git and not compared with the reference; runbooks prepared but never executed or confirmed by IT</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>EXT-13</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Updated runbook and scripts in git</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04, 07, 08</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3007,55 +3580,70 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>Screening</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Background checks for staff with privileged CKAM or server access</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
         <is>
           <t>R-04 (High)</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Confirm HR screening covers privileged staff (EXT-32)</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>HR screening records (sampled)</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr">
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 03</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3074,55 +3662,70 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>Terms and conditions of employment</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Security responsibilities in employment terms</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="inlineStr">
         <is>
           <t>R-04 (High)</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Add clause (EXT-32)</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>Contract template</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 03</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3141,55 +3744,70 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>Information security awareness, education and training</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED; docs/security/policies/10_Security_Awareness_Plan.md (DRAFT, no session held)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>NO TECH COMPONENT</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Annual awareness training; admin training on CKAM access control and incident reporting</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>HR; ISMS lead</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Not evidenced</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>R-05 (High), R-30 (Medium)</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>EXT-32</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Attendance records</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>NO TECH COMPONENT</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Annual awareness training; admin training on CKAM access control and incident reporting</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>HR; ISMS lead</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>Not evidenced</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>R-05 (High), R-30 (Medium)</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>EXT-32</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>Attendance records</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 10</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3208,55 +3826,70 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>Disciplinary process</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Disciplinary process covering security breaches</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="inlineStr">
         <is>
           <t>R-09 (Medium)</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Confirm HR policy</t>
         </is>
       </c>
-      <c r="L42" s="2" t="inlineStr">
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>HR policy</t>
         </is>
       </c>
-      <c r="M42" s="2" t="inlineStr">
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 03</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3275,55 +3908,70 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>Responsibilities after termination or change of employment</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/auth/tests.csv AU-T041..AU-T043; backend/tests/auth/test_vapt_sessions.py (AU-07 FIXED: token_version, migration f9a1c3e5b7d2)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>TECH READY: deactivation, switching off the login, and changes of role, work area, company access or password end the person's sessions at once (token_version); not yet deployed</t>
+          <t>docs/security/evidence/auth/tests.csv AU-T041..AU-T043; backend/tests/auth/test_vapt_sessions.py (AU-07 FIXED: token_version, migration f9a1c3e5b7d2); docs/security/policies/03_Joiner_Mover_Leaver_Procedure.md (DRAFT); backend/tests/auth/test_wpa2_token_version_atomic.py</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
+          <t>TECH READY: deactivation, switching off the login, and changes of role, work area, company access or password end the person's sessions at once (token_version); not yet deployed; closure: session version increment is atomic (OBS-TV) and ending a person's sessions also ends their server-side refresh sessions (auth_session); not deployed</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>Leaver/mover steps: switch off CKAM login on the last day, review role on transfer</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>HR; CKAM owner</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>No HR trigger to CKAM</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
         <is>
           <t>R-16 (Medium), R-19 (Medium)</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>EXT-33</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Leaver tickets with CKAM deactivation time</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 03</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3342,55 +3990,70 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
           <t>Confidentiality or non-disclosure agreements</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>NDAs for staff and contractors with access to CKAM data</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>HR; Legal</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
         <is>
           <t>R-11 (Medium)</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Confirm NDAs</t>
         </is>
       </c>
-      <c r="L44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>Signed NDAs (sample)</t>
         </is>
       </c>
-      <c r="M44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 03</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3409,55 +4072,70 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>ORGANISATIONAL</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>Remote working</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (public address via router port-forward of TCP 3211, plain HTTP)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (public address via router port-forward of TCP 3211, plain HTTP); docs/security/CKAM_HTTPS_IMPLEMENTATION_PLAN.md (prepared, owner decisions open)</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
           <t>TECH MISSING: anyone on the internet can reach the login page; no VPN; no TLS</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Remote access rule: VPN or HTTPS reverse proxy only</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>IT/Infra; Management</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>Remote access is open and unencrypted</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
         <is>
           <t>R-18 (Critical), R-01 (High)</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>EXT-05, EXT-04</t>
         </is>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Firewall/router config evidence</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -3476,55 +4154,70 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
           <t>Information security event reporting</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>frontend/src/features/support/report-problem-store.ts; backend/app/observability/client_reports.py; docs/security/evidence/auth/tests.csv AU-T098, AU-T101</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>TECH READY: Report a problem in the app with reference id; rate-limited</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Tell staff how to report a suspected security event (not only app errors)</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>ISMS lead; HR</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Channel for security events not communicated</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>R-27 (High)</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Include in awareness (EXT-32) and IR plan (EXT-20)</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>Communication record</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05, 10</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -3543,55 +4236,70 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
           <t>Physical security perimeters</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED (servers 10.0.1.98, 10.0.0.205 and NAS 10.0.0.25 are CityKart on-premise equipment)</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Defined secure perimeter for server room</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>Facilities; IT/Infra</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Confirm server-room controls (EXT-29)</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>Site inspection record</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr">
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3610,55 +4318,70 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
           <t>Physical entry</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Entry control and visitor log for server room</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Access log sample</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr">
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3677,55 +4400,70 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
           <t>Securing offices, rooms and facilities</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Secure rooms housing servers and NAS</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>Inspection record</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr">
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3744,55 +4482,70 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
           <t>Physical security monitoring</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>CCTV/alarm for server room</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>Monitoring records</t>
         </is>
       </c>
-      <c r="M50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3811,55 +4564,70 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
           <t>Protecting against physical and environmental threats</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Fire, flood, temperature protection for server room</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>Inspection record</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr">
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3878,55 +4646,70 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
           <t>Working in secure areas</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Rules for working in server room</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Facilities; IT</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>Procedure</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -3945,55 +4728,70 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
           <t>Clear desk and clear screen</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>backend/app/core/config.py (access token 15 minutes, refresh 8 hours)</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: short sessions; screen lock on shared store PCs not evidenced</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Clear-screen rule for store and office PCs</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>HR; IT</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Endpoint screen-lock not evidenced</t>
         </is>
       </c>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
         <is>
           <t>R-30 (Medium)</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>Include in acceptable use (EXT-17)</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Policy; GPO evidence</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr">
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 10</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4012,55 +4810,70 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
           <t>Equipment siting and protection</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Protect servers and NAS from damage and unauthorised access</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>Facilities; IT</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>Inspection record</t>
         </is>
       </c>
-      <c r="M54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4079,55 +4892,70 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
           <t>Security of assets off-premises</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>CKAM records custody of laptops and other assets given to employees (docs/ai/PRODUCT_CONTEXT.md)</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: CKAM shows who holds each device; device protection itself is outside CKAM</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Rules for laptops taken off-site (encryption, reporting loss: CKAM Report Lost)</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>IT; HR</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>Device protection rules not evidenced</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>R-25 (Medium)</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>Include in acceptable use (EXT-17)</t>
         </is>
       </c>
-      <c r="L55" s="2" t="inlineStr">
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>Policy; sample of encrypted devices</t>
         </is>
       </c>
-      <c r="M55" s="2" t="inlineStr">
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4146,55 +4974,70 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
           <t>Storage media</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (dumps on E: of 10.0.0.205; files on NAS); dev backups folder (IF-09)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (dumps on E: of 10.0.0.205; files on NAS); dev backups folder (IF-09); docs/security/CKAM_BACKUP_RESTORE_PLAN.md (prepared); docs/security/evidence/closure/infra/IF-09_ACL_PLAN.md (prepared; nothing changed on the dev PC)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
           <t>TECH MISSING: backup media not encrypted (IF-08)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Media handling and encryption rule for backups and exports</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Unencrypted backup media; dev dumps on dev PC</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
         <is>
           <t>R-13 (High), R-25 (Medium)</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>EXT-08, EXT-10</t>
         </is>
       </c>
-      <c r="L56" s="2" t="inlineStr">
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>Encryption evidence</t>
         </is>
       </c>
-      <c r="M56" s="2" t="inlineStr">
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 07</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -4213,55 +5056,70 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
           <t>Supporting utilities</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>UPS/power protection for servers and NAS</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>Facilities; IT</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>UPS test record</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr">
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4280,55 +5138,70 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
           <t>Cabling security</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Protect power and network cabling</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>Facilities</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L58" s="2" t="inlineStr">
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Inspection record</t>
         </is>
       </c>
-      <c r="M58" s="2" t="inlineStr">
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08 (inherited)</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4347,55 +5220,70 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>Equipment maintenance</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>CKAM records Under Repair / Send for Repair (docs/ai/DECISIONS.md 2026-10-14 (10))</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: CKAM tracks repairs of CityKart assets; server maintenance not evidenced</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Maintenance schedule for servers and NAS</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Not evidenced for CKAM servers</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
         <is>
           <t>R-28 (High)</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>Confirm</t>
         </is>
       </c>
-      <c r="L59" s="2" t="inlineStr">
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>Maintenance log</t>
         </is>
       </c>
-      <c r="M59" s="2" t="inlineStr">
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4414,55 +5302,70 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>PHYSICAL</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
           <t>Secure disposal or re-use of equipment</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>CKAM statuses Disposed / Scrapped / Sold (docs/ai/DECISIONS.md 2026-10-14 (2))</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: CKAM records disposal; data wiping before disposal is not recorded</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Wipe-before-disposal procedure with certificate; consider a CKAM remark or document upload of the certificate</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>IT; Facilities</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Wiping not evidenced</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="inlineStr">
         <is>
           <t>R-11 (Medium)</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>Procedure; attach wipe certificate to the asset in CKAM</t>
         </is>
       </c>
-      <c r="L60" s="2" t="inlineStr">
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>Disposal certificates</t>
         </is>
       </c>
-      <c r="M60" s="2" t="inlineStr">
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4481,55 +5384,70 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
           <t>User end point devices</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>docs/security (IF-09: dev PC .env and backups folder ACL)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
+          <t>docs/security (IF-09: dev PC .env and backups folder ACL); docs/security/evidence/closure/infra/IF-09_ACL_PLAN.md (plan only; NOTHING CHANGED on the dev PC)</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
           <t>TECH NOT EVIDENCED: store, office and phone endpoints not assessed; dev PC holds secrets and dumps</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Endpoint standard (patching, AV, disk encryption, screen lock)</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>Endpoints not evidenced; dev PC ACL gap</t>
         </is>
       </c>
-      <c r="J61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="inlineStr">
         <is>
           <t>R-25 (Medium)</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>EXT-10, EXT-37</t>
         </is>
       </c>
-      <c r="L61" s="2" t="inlineStr">
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>Endpoint compliance report</t>
         </is>
       </c>
-      <c r="M61" s="2" t="inlineStr">
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4548,55 +5466,70 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
           <t>Privileged access rights</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/access/tests.csv (escalation cases); docs/security/evidence/infra/db_01_roles_privileges.out.txt (dev role superuser); docs/ai/PRODUCTION_INFRASTRUCTURE.md (prod role ckassetapp not superuser; task runs as SYSTEM)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: head-office admin grants audited; Full Admin cannot touch head-office admin; but no MFA, Full Admin works in every company (D6), runtime DB role owns the tables, service runs as SYSTEM (IF-07)</t>
+          <t>docs/security/evidence/access/tests.csv (escalation cases); docs/security/evidence/infra/db_01_roles_privileges.out.txt (dev role superuser); docs/ai/PRODUCTION_INFRASTRUCTURE.md (prod role ckassetapp not superuser; task runs as SYSTEM); ops/db/role_split.sql, role_split_verify.sql, check_least_privilege.sql; docs/security/evidence/closure/db/WPB_RESULTS.md (runtime role: 7/7 needed actions work, 40/40 forbidden refused; verify 45/45; 34 least-privilege checks); docs/security/CKAM_SERVICE_ACCOUNT_PLAN.md</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: head-office admin grants audited; Full Admin cannot touch head-office admin; but no MFA, Full Admin works in every company (D6), runtime DB role owns the tables, service runs as SYSTEM (IF-07); closure: role split designed and proven locally (sequences USAGE/SELECT only after CL2-IF-01; RESET ALL after CL2-IF-02); dev/api containers non-root (IF-13 FIXED); in production still owner = runtime role and SYSTEM service</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
           <t>Privileged access register and review; MFA decision</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>CKAM owner; IT/Infra; DBA</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>Privileged paths not minimised</t>
-        </is>
-      </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
+          <t>Privileged paths not minimised in production: role split not run on 10.0.0.205 (EXT-07, EXT-45), service still SYSTEM (EXT-06), no MFA, D6 open</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
           <t>R-04 (High), R-07 (High), R-12 (Medium)</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>EXT-06, EXT-07, EXT-19, EXT-26</t>
         </is>
       </c>
-      <c r="L62" s="2" t="inlineStr">
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>Privileged access register</t>
         </is>
       </c>
-      <c r="M62" s="2" t="inlineStr">
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02, 11</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4615,55 +5548,70 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
           <t>Information access restriction</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/access/tests.csv (208 IDOR/BOLA cases, 4 cross-company cases); docs/security/evidence/access/self_service_masters.txt; docs/security/evidence/infra/erp_cross_company_draft.txt; backend/tests/core/test_security_read_scope.py; docs/security/CKAM_SECURITY_REMEDIATION_REPORT.md</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>TECH READY: company, work-area and own-custody scoping on every read; AC-1, AC-2 and IF-03 FIXED and retested (local commits)</t>
+          <t>docs/security/evidence/access/tests.csv (208 IDOR/BOLA cases, 4 cross-company cases); docs/security/evidence/access/self_service_masters.txt; docs/security/evidence/infra/erp_cross_company_draft.txt; backend/tests/core/test_security_read_scope.py; docs/security/CKAM_SECURITY_REMEDIATION_REPORT.md; docs/security/evidence/closure/retest2/access/authz_matrix.csv and tests.csv (319 cases, 0 escalations on the final code)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
+          <t>TECH READY: company, work-area and own-custody scoping on every read; AC-1, AC-2 and IF-03 FIXED and retested (local commits); retested twice more in the closure stage</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
           <t>None beyond policy</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>Fixes not yet deployed; production 3b5e842 still has AC-1, AC-2, IF-03</t>
-        </is>
-      </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
+          <t>Only deployment is missing: production 3b5e842 still has AC-1, AC-2 and IF-03 (counted PARTIAL for production readiness)</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
           <t>R-10 (Medium)</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Deploy (EXT-01); becomes READY on deploy</t>
-        </is>
-      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
+          <t>Deploy (EXT-01); becomes READY after the post-deploy check</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
           <t>Deploy record + post-deploy check</t>
         </is>
       </c>
-      <c r="M63" s="2" t="inlineStr">
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>READY IN CODE - NOT DEPLOYED</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4682,55 +5630,70 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
           <t>Access to source code</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>git remote origin (GitHub, personal account); 286 commits by one author; secrets scan: none in working tree or 282 commits</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>TECH NOT EVIDENCED: repository visibility, collaborator list and MFA unknown</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Company-owned repository, MFA, least access, branch protection</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>Management; Dev lead</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>Repository control not evidenced</t>
         </is>
       </c>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="inlineStr">
         <is>
           <t>R-26 (Medium)</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>EXT-28</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>Repository settings evidence</t>
         </is>
       </c>
-      <c r="M64" s="2" t="inlineStr">
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02, 04</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -4749,55 +5712,70 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
           <t>Secure authentication</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/auth/tests.csv (original 102 cases); backend/tests/auth/test_vapt_login.py, test_rate_limit.py, test_vapt_sessions.py, test_vapt_password_policy.py; docs/security/CKAM_SECURITY_REMEDIATION_REPORT.md</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: Argon2id, HS256 pinned, alg:none and tampering rejected, lockout, constant-time sign-in (AU-01), rate limit 429 (AU-03), revocable sessions (AU-05, AU-07), password policy (AU-08) all FIXED; AU-06 MITIGATED; still open: IF-02 plain HTTP, no MFA; none of the fixes deployed yet</t>
+          <t>docs/security/evidence/auth/tests.csv (original 102 cases); backend/tests/auth/test_vapt_login.py, test_rate_limit.py, test_vapt_sessions.py, test_vapt_password_policy.py; docs/security/CKAM_SECURITY_REMEDIATION_REPORT.md; backend/tests/auth/test_wpa2_refresh_reuse.py; backend/tests/auth/test_wpa2_token_version_atomic.py; migration b5d7f9a1c3e5_auth_session_refresh_reuse.py; docs/security/evidence/closure/retest2/sessions/RETEST2_SESSIONS.md (56 cases, all PASS)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: Argon2id, HS256 pinned, alg:none and tampering rejected, lockout, constant-time sign-in (AU-01), rate limit 429 (AU-03), revocable sessions (AU-05, AU-07), password policy (AU-08) all FIXED; AU-06 MITIGATED; still open: IF-02 plain HTTP, no MFA; none of the fixes deployed yet; closure: AU-06 FIXED (server-side auth_session with SHA-256 of the token id, rotate-once, 10 s grace, reuse =&gt; 401 + every session of that person ended + REFRESH_REUSE audit row); atomic token_version (OBS-TV); still open: IF-02 plain HTTP, no MFA, no absolute session lifetime (decision); nothing deployed</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
           <t>MFA decision; password policy document</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>Dev lead; IT</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>Plain HTTP; no MFA; fixes not deployed</t>
-        </is>
-      </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
+          <t>Plain HTTP; no MFA; no absolute session lifetime decision; fixes not deployed</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
           <t>R-05 (High), R-01 (High), R-19 (Medium)</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>EXT-01, EXT-04, EXT-19</t>
         </is>
       </c>
-      <c r="L65" s="2" t="inlineStr">
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>Deploy record; HTTPS scan</t>
         </is>
       </c>
-      <c r="M65" s="2" t="inlineStr">
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4816,55 +5794,70 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
           <t>Capacity management</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md (slow request/SQL rows, 660 MB log cap, GET /api/admin/diagnostics/db)</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: slow operations recorded; request-size limits protect memory (N1 FIXED: 64 KB sign-in, 5 MB JSON, 16 MB uploads); no capacity thresholds or alerts</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Monthly capacity review (disk on 10.0.1.98, 10.0.0.205, NAS)</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>No capacity monitoring</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>R-21 (Medium)</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>EXT-22</t>
         </is>
       </c>
-      <c r="L66" s="2" t="inlineStr">
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>Capacity review records</t>
         </is>
       </c>
-      <c r="M66" s="2" t="inlineStr">
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4883,55 +5876,70 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
           <t>Protection against malware</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>docs/security/evidence/input/raw_sql_review.md section 8; backend/tests/documents/test_vapt_content_check.py (IN-03 FIXED: file-signature check)</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>TECH PARTIAL: uploads restricted by extension, file signature and size, served as attachment with nosniff; no AV scan of uploads; server AV not evidenced</t>
-        </is>
-      </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: uploads restricted by extension, file signature and size, served as attachment with nosniff; no AV scan of uploads; server AV not evidenced; a polyglot document (PDF header + HTML body) passes the prefix-only content check but is only ever served as attachment + nosniff (INFO, not exploitable)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
           <t>Antimalware/EDR on servers and NAS</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>Server and NAS malware protection not evidenced</t>
         </is>
       </c>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="inlineStr">
         <is>
           <t>R-14 (High), R-22 (Low)</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>EXT-37</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>EDR console evidence</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr">
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 06</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -4950,55 +5958,70 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>Management of technical vulnerabilities</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/ (VAPT 2026-10-15); docs/security/evidence/infra/dependency_audit.md; docs/security/evidence/infra/static_route_traversal_and_startup.txt</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: every code finding fixed or mitigated and retested within the programme (646 + 310 retest cases, 0 original findings left unretested), but all fixes are local commits; production still runs the vulnerable release 3b5e842</t>
+          <t>docs/security/evidence/ (VAPT 2026-10-15); docs/security/evidence/infra/dependency_audit.md; docs/security/evidence/infra/static_route_traversal_and_startup.txt; docs/security/CKAM_SECURITY_CLOSURE_REGISTER.md; docs/security/evidence/closure/retest1/RETEST1.md (137 cases); docs/security/evidence/closure/retest2/ (497 cases: access 319, infra 122, sessions 56)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: every code finding fixed or mitigated and retested within the programme (646 + 310 retest cases, 0 original findings left unretested), but all fixes are local commits; production still runs the vulnerable release 3b5e842; closure: every code-fixable Critical/High/Medium item fixed and independently retested locally (retest 1: 137 cases; retest 2: 497 cases; new findings CL2-IF-01..04 fixed in ca94574); production still runs 3b5e842 with IF-01 and the QR deep-link bug (CL2-IF-04)</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
           <t>Vulnerability management procedure with severity SLAs; OS patching</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>Dev lead; IT/Infra</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>CRITICAL IF-01 still exposed in production until deploy + secret rotation; no scheduled scanning or SLA</t>
-        </is>
-      </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
+          <t>CRITICAL IF-01 still exposed in production until deploy + secret rotation; no scheduled scanning; SLAs only in DRAFT doc 06</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
           <t>R-02 (Critical), R-17 (High), R-15 (Medium)</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>EXT-01, EXT-09, EXT-14</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Deploy record; scan schedule; SLA</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 06</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5017,55 +6040,70 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>Configuration management</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>.env.example; backend/app/core/config.py; docs/ai/CKAM_PRODUCTION_ENVIRONMENT_CHECKLIST.md; backend/tests/core/test_production_secret_guard.py; backend/tests/test_vapt_headers_and_docs.py</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: settings centralised; production refuses a weak JWT secret (IF-04 FIXED) and any unknown ENVIRONMENT_NAME counts as production (N4 FIXED); /docs off in production (IF-14 FIXED); but production launcher and release script not in git (IF-15) and uvicorn trusts X-Forwarded-For from 127.0.0.1 (N2, needs --no-proxy-headers)</t>
+          <t>.env.example; backend/app/core/config.py; docs/ai/CKAM_PRODUCTION_ENVIRONMENT_CHECKLIST.md; backend/tests/core/test_production_secret_guard.py; backend/tests/test_vapt_headers_and_docs.py; frontend/scripts/check-nginx-live.mjs; frontend/src/security/nginx-config.test.ts; backend/tests/core/test_n2_forwarded_for.py; ops/windows/run_ckam_web.ps1.template</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: settings centralised; production refuses a weak JWT secret (IF-04 FIXED) and any unknown ENVIRONMENT_NAME counts as production (N4 FIXED); /docs off in production (IF-14 FIXED); but production launcher and release script not in git (IF-15) and uvicorn trusts X-Forwarded-For from 127.0.0.1 (N2, needs --no-proxy-headers); closure: unset ENVIRONMENT_NAME now means production (CL1-N4-01, fails closed); security headers exactly once (N5); every repository launch path starts uvicorn with --no-proxy-headers --no-server-header (N2); reference launcher in ops/windows; the production launcher still needs these flags (EXT-38) and is not in git (EXT-13)</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
           <t>Configuration baseline for servers and app; change log of shared\.env</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>IT/Infra; Dev lead</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Server configuration not baselined</t>
         </is>
       </c>
-      <c r="J69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="inlineStr">
         <is>
           <t>R-23 (High), R-20 (Medium)</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>EXT-13</t>
         </is>
       </c>
-      <c r="L69" s="2" t="inlineStr">
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>Baseline document</t>
         </is>
       </c>
-      <c r="M69" s="2" t="inlineStr">
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5084,55 +6122,70 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
           <t>Information deletion</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>CLAUDE.md rule 2 (soft-deactivate only); docs/ai/LOGGING_AND_DIAGNOSTICS.md section 4 (error/system/client rows purged after 180 days; audit kept forever; guarded purge)</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: controlled log purge; no business-data deletion (by design)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Retention schedule; procedure for deleting PII when legally required</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>Management; Legal</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>No retention schedule for business data or audit</t>
         </is>
       </c>
-      <c r="J70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="inlineStr">
         <is>
           <t>R-31 (Medium), R-11 (Medium)</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>EXT-21, EXT-31</t>
         </is>
       </c>
-      <c r="L70" s="2" t="inlineStr">
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>Retention schedule</t>
         </is>
       </c>
-      <c r="M70" s="2" t="inlineStr">
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01, 07</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5151,55 +6204,70 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
           <t>Data masking</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>backend/app/observability/redact.py; backend/tests/observability/test_redaction.py; docs/security/evidence/auth/tests.csv AU-T049, AU-T089, AU-T090</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>TECH READY: secrets, tokens, hashes and passwords masked in every log, audit row and diagnostics bundle; SQL literals replaced by ?</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
+          <t>TECH READY: secrets, tokens, hashes and passwords masked in every log, audit row and diagnostics bundle; SQL literals replaced by ?; closure: refresh-token ids are stored only as SHA-256 hashes, never raw</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
           <t>None (PII is shown to authorised admins by design)</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>None for secret masking</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="inlineStr">
         <is>
           <t>R-03 (Critical)</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>Keep redaction tests in the suite</t>
         </is>
       </c>
-      <c r="L71" s="2" t="inlineStr">
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>Test output</t>
         </is>
       </c>
-      <c r="M71" s="2" t="inlineStr">
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -5218,55 +6286,70 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
           <t>Data leakage prevention</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md (EXPORT rows); main.py Cache-Control no-store on /api/</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: exports role-restricted and audited; no DLP; plain HTTP</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Export handling rules</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>ISMS lead</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>No DLP; transport not encrypted</t>
         </is>
       </c>
-      <c r="J72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="inlineStr">
         <is>
           <t>R-11 (Medium), R-01 (High)</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>EXT-04, EXT-17</t>
         </is>
       </c>
-      <c r="L72" s="2" t="inlineStr">
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>Policy; export audit review</t>
         </is>
       </c>
-      <c r="M72" s="2" t="inlineStr">
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5285,55 +6368,70 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
           <t>Information backup</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (task CK_Backup_CKASSETMANAGEMENT, daily 03:00, 30 days, on the DB server); ops/backup.sh (dev); docs/ai/AM-09_RC_FULL_AUDIT_REPORT.md (dev restore drill)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (task CK_Backup_CKASSETMANAGEMENT, daily 03:00, 30 days, on the DB server); ops/backup.sh (dev); docs/ai/AM-09_RC_FULL_AUDIT_REPORT.md (dev restore drill); docs/security/CKAM_BACKUP_RESTORE_PLAN.md (prepared); docs/security/policies/07_Backup_Restore_Policy.md (DRAFT)</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: daily DB dump; not copied off the DB server, not encrypted, never restored in production; NAS document backup not evidenced (IF-08)</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Backup policy; quarterly restore test; off-server encrypted copy</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Single-location unencrypted backups</t>
         </is>
       </c>
-      <c r="J73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="inlineStr">
         <is>
           <t>R-13 (High), R-14 (High)</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>EXT-08</t>
         </is>
       </c>
-      <c r="L73" s="2" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Restore drill report; off-site copy log</t>
         </is>
       </c>
-      <c r="M73" s="2" t="inlineStr">
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 07</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5352,55 +6450,70 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>Redundancy of information processing facilities</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (one app server, one DB server)</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>TECH MISSING: no redundancy; auto-restart only</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Decide availability need; document accepted risk or add standby</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>Management; IT/Infra</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>No redundancy and no documented acceptance</t>
         </is>
       </c>
-      <c r="J74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="inlineStr">
         <is>
           <t>R-13 (High)</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>Record risk acceptance in BCP (EXT-29)</t>
         </is>
       </c>
-      <c r="L74" s="2" t="inlineStr">
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>Risk acceptance</t>
         </is>
       </c>
-      <c r="M74" s="2" t="inlineStr">
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 08</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
         <is>
           <t>MISSING</t>
         </is>
@@ -5419,55 +6532,70 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>Logging</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md; docs/security/evidence/auth/audit_coverage.csv (122 write routes: 107 audited, 15 intentionally not, 0 accidental); docs/security/evidence/auth/tests.csv AU-T086..AU-T097</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: complete application logging with request ids and redaction; TRUNCATE guards and purge floor added (IF-05/IF-06 MITIGATED); owner can still drop triggers; logs only on the app/DB servers; PostgreSQL slow/lock logging not applied in production</t>
+          <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md; docs/security/evidence/auth/audit_coverage.csv (122 write routes: 107 audited, 15 intentionally not, 0 accidental); docs/security/evidence/auth/tests.csv AU-T086..AU-T097; backend/app/observability/writer.py; backend/tests/observability/test_log_write_failure_reporting.py</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: complete application logging with request ids and redaction; TRUNCATE guards and purge floor added (IF-05/IF-06 MITIGATED); owner can still drop triggers; logs only on the app/DB servers; PostgreSQL slow/lock logging not applied in production; closure (not deployed): new SECURITY events REFRESH_REUSE, REFRESH_DUPLICATE, RATE_LIMITED next to LOGIN_FAILED and INVALID_TOKEN; a failed log/audit write is reported at once and then at most once a minute with a count (kind log_write_failed); X-Request-ID also on nginx answers (dev); log retention still 180 days</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
           <t>Log review and retention procedure</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>Dev lead; IT/Infra</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Logs not protected or shipped off-server</t>
-        </is>
-      </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
+          <t>Logs not protected or shipped off-server; 180-day retention of error/system/client rows; nothing of the closure deployed</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
           <t>R-12 (Medium), R-27 (High)</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>EXT-07, EXT-21, EXT-27</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>Log shipping evidence</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5486,55 +6614,70 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
           <t>Monitoring activities</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/LOGGING_AND_DIAGNOSTICS.md section 8 (admin log screens, diagnostics); Home error count (commit 4ba4e94)</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>TECH PARTIAL: data to monitor exists; no alerting and no review schedule</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: data to monitor exists; no alerting and no review schedule; closure: audit-write failures and refresh-token reuse now produce rows/lines to alert on, but no alerting exists (EXT-22, EXT-48)</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
           <t>Weekly review of security events; alerts for lockouts, 5xx spikes, backup failure, ERP sync failure</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>IT; CKAM owner</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>No active monitoring</t>
         </is>
       </c>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="inlineStr">
         <is>
           <t>R-27 (High)</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>EXT-22</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>Alert configuration; review log</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr">
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 05</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5553,55 +6696,70 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
           <t>Clock synchronization</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>NOT EVIDENCED (application stores timezone-aware UTC timestamps)</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>TECH NOT EVIDENCED: NTP on 10.0.1.98, 10.0.0.205, NAS not checked</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Time source standard for all servers</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="inlineStr">
         <is>
           <t>R-12 (Medium)</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>Confirm NTP configuration</t>
         </is>
       </c>
-      <c r="L77" s="2" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>w32tm status output</t>
         </is>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 06</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -5620,55 +6778,70 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
           <t>Use of privileged utility programs</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (superuser DB steps typed by the user); docs/ai/LOGGING_AND_DIAGNOSTICS.md (diagnostics read-only, head-office admin only, audited)</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>TECH NOT EVIDENCED: who can run psql/pgAdmin or PowerShell as admin on the servers is not recorded</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Restrict and log use of DB superuser and server admin tools</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>IT/Infra; DBA</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>Not evidenced</t>
         </is>
       </c>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="inlineStr">
         <is>
           <t>R-12 (Medium), R-06 (High)</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>Privileged access register (EXT-18)</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Register; logs</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr">
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 02</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -5687,55 +6860,70 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
           <t>Installation of software on operational systems</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (pip install -e into shared\venv at deploy); backend/constraints.txt (IF-11 file added)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (pip install -e into shared\venv at deploy); backend/constraints.txt (IF-11 file added); ops/windows/deploy_ckam.ps1.template (pip install -c constraints.txt; reference only, never run on the server)</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: only approved releases are installed by the owner; a constraints file now exists but the production install does not use it yet</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Locked, reviewed installs; record of installed packages per release</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>Dev lead; IT</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>Unpinned Python installs</t>
         </is>
       </c>
-      <c r="J79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="inlineStr">
         <is>
           <t>R-15 (Medium)</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>EXT-12</t>
         </is>
       </c>
-      <c r="L79" s="2" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>pip freeze per release</t>
         </is>
       </c>
-      <c r="M79" s="2" t="inlineStr">
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04, 06</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5754,55 +6942,70 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
           <t>Networks security</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (pg_hba allows ckassetapp only from 10.0.1.98/32; firewall rule CKAM-Web TCP 3211; router forwards 3211 from the internet)</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>TECH PARTIAL: DB access restricted by host; app exposed to the internet over HTTP; ERP link without TLS (IF-16)</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: DB access restricted by host; app exposed to the internet over HTTP; ERP link without TLS (IF-16); dev/UAT only: nginx overwrites X-Forwarded-For and the API trusts only nginx's fixed address (N3); production unchanged (plain HTTP, internet forward)</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
           <t>Network security standard</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>Internet exposure without TLS</t>
         </is>
       </c>
-      <c r="J80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="inlineStr">
         <is>
           <t>R-18 (Critical), R-01 (High), R-08 (Medium)</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>EXT-04, EXT-05, EXT-25</t>
         </is>
       </c>
-      <c r="L80" s="2" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>Network diagram; firewall export</t>
         </is>
       </c>
-      <c r="M80" s="2" t="inlineStr">
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01, 02</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5821,55 +7024,70 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
           <t>Security of network services</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: services identified (HTTP 3211, PostgreSQL 5432, SMB to NAS, ERP 5432); ERP reads now time-limited (IF-10 FIXED); no TLS on any of them evidenced; uvicorn trusts X-Forwarded-For from 127.0.0.1 (N2)</t>
+          <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md; backend/tests/erp/test_erp_tls_settings.py; backend/tests/core/test_n2_forwarded_for.py</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: services identified (HTTP 3211, PostgreSQL 5432, SMB to NAS, ERP 5432); ERP reads now time-limited (IF-10 FIXED); no TLS on any of them evidenced; uvicorn trusts X-Forwarded-For from 127.0.0.1 (N2); closure: ERP connection TLS settable (PO_SOURCE_SSLMODE / PO_SOURCE_SSLROOTCERT, default prefer = today, TLS not mandatory; ERP owner must confirm TLS); N2 code side done (repository launch paths), production launcher still needs --no-proxy-headers (EXT-38)</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
           <t>Define security requirements per network service; run uvicorn with --no-proxy-headers</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>No TLS; no service hardening record; N2 open</t>
-        </is>
-      </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
+          <t>No TLS on any production link; production launcher flag (N2) not applied; no service hardening record</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
           <t>R-01 (High), R-08 (Medium)</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>EXT-04, EXT-25</t>
         </is>
       </c>
-      <c r="L81" s="2" t="inlineStr">
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>Service inventory with controls</t>
         </is>
       </c>
-      <c r="M81" s="2" t="inlineStr">
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01, 02</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5888,55 +7106,70 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
           <t>Segregation of networks</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/PRODUCTION_INFRASTRUCTURE.md (shared servers with Spinwheel and Citykart Desk)</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>TECH NOT EVIDENCED: VLAN/segmentation not documented</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Separate server network from user network; isolate internet-facing service</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>IT/Infra</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Not evidenced; shared hosts</t>
         </is>
       </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="inlineStr">
         <is>
           <t>R-06 (High), R-18 (Critical)</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>EXT-24, EXT-05</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>Network diagram</t>
         </is>
       </c>
-      <c r="M82" s="2" t="inlineStr">
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>NOT EVIDENCED</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
         <is>
           <t>NOT EVIDENCED</t>
         </is>
@@ -5955,55 +7188,70 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
           <t>Web filtering</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Not applicable to the CKAM application: outbound web filtering is a CityKart corporate network control outside this scope</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>NO TECH COMPONENT</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>None for CKAM</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>IT (corporate)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="L83" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6022,55 +7270,70 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
           <t>Use of cryptography</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>docs/security/evidence/auth/tests.csv AU-T017..AU-T021, AU-T044; backend/app/core/security.py (HS256 pinned)</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>TECH PARTIAL: strong password hashing and signed tokens; no TLS for browser, ERP or DB links evidenced; backups unencrypted; no key rotation procedure</t>
-        </is>
-      </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: strong password hashing and signed tokens; no TLS for browser, ERP or DB links evidenced; backups unencrypted; no key rotation procedure; closure: refresh-token ids hashed with SHA-256; ERP TLS settable but not mandatory (IF-16 code side)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
           <t>Cryptography and key-management policy (JWT secret rotation, certificate renewal)</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>IT/Infra; Dev lead</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>No encryption in transit; no key management</t>
         </is>
       </c>
-      <c r="J84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="inlineStr">
         <is>
           <t>R-01 (High), R-03 (Critical), R-13 (High)</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>EXT-02, EXT-04, EXT-08, EXT-25</t>
         </is>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>Policy; TLS scan; key-rotation record</t>
         </is>
       </c>
-      <c r="M84" s="2" t="inlineStr">
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6089,55 +7352,70 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
           <t>Secure development life cycle</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/DEVELOPMENT_GUARDRAILS.md; CLAUDE.md (test before commit, Alembic only); docs/security/CKAM_SECURITY_BASELINE.md</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>TECH PARTIAL: test-before-commit rule; security rules added to docs/ai/DEVELOPMENT_GUARDRAILS.md (da790d1); no CI pipeline, no SAST, unsigned commits, single author (IF-17)</t>
+          <t>docs/ai/DEVELOPMENT_GUARDRAILS.md; CLAUDE.md (test before commit, Alembic only); docs/security/CKAM_SECURITY_BASELINE.md; docs/security/CKAM_SECURITY_BASELINE.md (closure rules added 2026-10-16); frontend/scripts/check-build-security.mjs (npm run check:build)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: test-before-commit rule; security rules added to docs/ai/DEVELOPMENT_GUARDRAILS.md (da790d1); no CI pipeline, no SAST, unsigned commits, single author (IF-17); closure: permanent build/nginx security checks (check:build, check:nginx-live, nginx config test) and a least-privilege pytest added; still no CI, unsigned commits, single author (IF-17)</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
           <t>Secure development policy; CI with tests and dependency audit</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>Rules depend on discipline, not automation</t>
         </is>
       </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="inlineStr">
         <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>EXT-28 (CI), adopt baseline</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>CI run history</t>
         </is>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6156,55 +7434,70 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
           <t>Application security requirements</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>docs/ai/DEVELOPMENT_GUARDRAILS.md; docs/ai/DECISIONS.md (authorization, append-only, ERP read-only decisions); docs/security/CKAM_SECURITY_BASELINE.md</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
+          <t>docs/ai/DEVELOPMENT_GUARDRAILS.md; docs/ai/DECISIONS.md (authorization, append-only, ERP read-only decisions); docs/security/CKAM_SECURITY_BASELINE.md; docs/security/CKAM_SECURITY_BASELINE.md updated 2026-10-16 (still not approved)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: requirements documented; security rules committed to the guardrails (da790d1) and point to the baseline; baseline not yet approved by the owner</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Approve baseline as mandatory requirements</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>Dev lead; Management</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>Baseline not yet approved</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="inlineStr">
         <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>Approve the baseline</t>
         </is>
       </c>
-      <c r="L86" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>Approved baseline</t>
         </is>
       </c>
-      <c r="M86" s="2" t="inlineStr">
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6223,55 +7516,70 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
           <t>Secure system architecture and engineering principles</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>docs/security/CKAM_THREAT_MODEL.md; docs/ai/DECISIONS.md 2026-10-14 (1),(6),(7); backend/app/lifecycle/service.py (single writer)</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>TECH PARTIAL: backend-authoritative, single writer of asset status, append-only ledger, ERP via local read-only copy, same-origin; but single-port uvicorn without TLS, SYSTEM service, owner=runtime DB role</t>
-        </is>
-      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
+          <t>TECH PARTIAL: backend-authoritative, single writer of asset status, append-only ledger, ERP via local read-only copy, same-origin; but single-port uvicorn without TLS, SYSTEM service, owner=runtime DB role; closure: owner/migrator/runtime DB role design (proven locally), DB guard on lifecycle fields, single-port SPA fallback that serves app pages without touching the filesystem for unknown paths; production unchanged</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
           <t>Architecture review for each new component</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Runtime privilege and transport design weak</t>
         </is>
       </c>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="inlineStr">
         <is>
           <t>R-07 (High), R-01 (High)</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>EXT-04, EXT-06, EXT-07</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>Architecture review record</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr">
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6290,55 +7598,70 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
           <t>Secure coding</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/input/raw_sql_review.md; docs/security/evidence/input/tests.csv; docs/security/evidence/input/xss_results.json; docs/security/evidence/input/formula_export_cell.txt; backend/tests/test_static_frontend.py; backend/tests/core/test_security_concurrency.py; docs/ai/DEVELOPMENT_GUARDRAILS.md (file-path and file-security rules)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>TECH READY: SQL injection, XSS, formula injection, SSRF, command injection and unsafe deserialization safe; path containment (IF-01), bounded imports (IN-02), same-name creation race (RACE-1) FIXED and retested; file-security rules in the guardrails</t>
+          <t>docs/security/evidence/input/raw_sql_review.md; docs/security/evidence/input/tests.csv; docs/security/evidence/input/xss_results.json; docs/security/evidence/input/formula_export_cell.txt; backend/tests/test_static_frontend.py; backend/tests/core/test_security_concurrency.py; docs/ai/DEVELOPMENT_GUARDRAILS.md (file-path and file-security rules); backend/tests/test_static_frontend_windows.py and test_static_frontend_spa_assets.py (IF-01-WIN lexical refusal before any filesystem call; CL2-IF-04 deep links); docs/security/evidence/closure/windows/ (native Windows run: old code leaked fake canaries in 10 of 28 payloads, fixed code 0 of 28); backend/tests/masters/test_wpf2_category_names.py; backend/tests/core/test_wpf2_serial_race_message.py</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
+          <t>TECH READY: SQL injection, XSS, formula injection, SSRF, command injection and unsafe deserialization safe; path containment (IF-01), bounded imports (IN-02), same-name creation race (RACE-1) FIXED and retested; file-security rules in the guardrails; closure: lexical Windows-path refusal, atomic counters, advisory lock + check for unique names (vendor, brand, category/sub-category), no raw token ids stored</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
           <t>Keep the file-security review rule</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>Production still runs code without these fixes (tracked under A.8.8 / EXT-01)</t>
         </is>
       </c>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="K88" s="2" t="inlineStr">
         <is>
           <t>R-02 (Critical), R-21 (Medium)</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>Deploy (EXT-01)</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Deploy record</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr">
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04, 06</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -6357,55 +7680,70 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
           <t>Security testing in development and acceptance</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/access/tests.csv; docs/security/evidence/auth/tests.csv; docs/security/evidence/input/tests.csv; backend/tests/observability/test_coverage_walker.py; backend/tests/test_static_frontend.py; backend/tests/**/test_vapt_*.py; frontend/e2e/security.spec.ts; docs/ai/CKAM_FINAL_UAT.md; docs/security/CKAM_VAPT_REPORT.md</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>TECH READY: security regression tests run before every commit; original VAPT battery (636 cases) plus final retest (646 + 310 cases, 0 original findings left unretested); backend about 1,783 tests (final run number from the lead), frontend 1,239 tests in 90 files, Playwright security journeys 14/14 and 11 permanent journeys (1 skipped: ERP link off on the test stack)</t>
+          <t>docs/security/evidence/access/tests.csv; docs/security/evidence/auth/tests.csv; docs/security/evidence/input/tests.csv; backend/tests/observability/test_coverage_walker.py; backend/tests/test_static_frontend.py; backend/tests/**/test_vapt_*.py; frontend/e2e/security.spec.ts; docs/ai/CKAM_FINAL_UAT.md; docs/security/CKAM_VAPT_REPORT.md; docs/security/evidence/closure/retest1/, docs/security/evidence/closure/retest2/, docs/security/evidence/closure/perf/PERF_REPORT.md, docs/security/evidence/closure/windows/</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
+          <t>TECH READY: security regression tests run before every commit; original VAPT battery (636 cases) plus final retest (646 + 310 cases, 0 original findings left unretested); backend about 1,783 tests (final run number from the lead), frontend 1,239 tests in 90 files, Playwright security journeys 14/14 and 11 permanent journeys (1 skipped: ERP link off on the test stack); final local regression (HEAD fd34520): backend 2541 passed, 1 skipped; frontend tsc clean, vitest 1257 passed in 92 files, build + check:build OK; Playwright permanent journeys 11 passed, 1 skipped; security journeys 14/14; closure retests 137 + 497 cases; performance before/after 31 operations none over threshold (supersedes the 2026-10-15 numbers)</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
           <t>Repeat the VAPT battery before each major release</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>Dev lead</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>No schedule yet for repeating the battery</t>
         </is>
       </c>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>Add battery re-run to release checklist</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="M89" s="2" t="inlineStr">
         <is>
           <t>Release test record</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr">
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04, 06</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -6424,55 +7762,70 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>Outsourced development</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
-        </is>
-      </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>git log (275 of 286 commits co-authored by an AI coding assistant); no external development firm evidenced</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: every change is tested and the owner approves push and deploy; production passwords are typed by the user, never into chat (docs/ai/ERP_INTEGRATION.md, CLAUDE.md)</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Rules for AI-assisted development: what data may be shared with the tool, mandatory human review</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>Management; Dev lead</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>No written rule for AI-assisted development</t>
         </is>
       </c>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="K90" s="2" t="inlineStr">
         <is>
           <t>R-23 (High), R-03 (Critical)</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>Add AI-assisted development section to secure development policy (EXT-17)</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04, 09</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6491,55 +7844,70 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
+          <t>TECHNICAL</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
           <t>Separation of development, test and production environments</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>CLAUDE.md (dev 10.0.0.47; prod 10.0.1.98 / 10.0.0.205 / NAS); backend/tests/conftest.py (refuses the plain ckam DB); docs/ai/CKAM_PRODUCTION_ENVIRONMENT_CHECKLIST.md (independent production secrets required)</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>TECH READY: separate machines, databases and settings; tests run on ckam_test only</t>
-        </is>
-      </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
+          <t>TECH READY: separate machines, databases and settings; tests run on ckam_test only; closure: an unset ENVIRONMENT_NAME now counts as production (fails closed)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
           <t>Keep production secrets independent of dev (not re-evidenced)</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>Dev lead; IT</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>Independence of production secrets not re-verified</t>
         </is>
       </c>
-      <c r="J91" s="2" t="inlineStr">
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>R-03 (Critical)</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>Confirm during rotation (EXT-02)</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>Rotation record</t>
         </is>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
@@ -6558,55 +7926,70 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
           <t>Change management</t>
         </is>
       </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>CLAUDE.md (commit, then user-approved push, then separately approved deploy); docs/ai/PRODUCTION_INFRASTRUCTURE.md (backup first, release by sha, alembic, verify, rollback)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
+          <t>CLAUDE.md (commit, then user-approved push, then separately approved deploy); docs/ai/PRODUCTION_INFRASTRUCTURE.md (backup first, release by sha, alembic, verify, rollback); docs/security/policies/04_Change_Management_Procedure.md and templates/change_record.md (DRAFT, no record yet); 22 local security commits waiting for the owner's push approval (none pushed, none deployed)</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
           <t>TECH PARTIAL: release folder per commit, verification steps, rollback folders kept; the 8 security commits stay local until the owner approves push and deploy; no change ticket, no recorded approver, launcher not in git (IF-15)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Change record per release (request id, approver, tests, rollback plan, result)</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
         <is>
           <t>Dev lead; CKAM owner</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>Approvals and results not recorded as evidence</t>
         </is>
       </c>
-      <c r="J92" s="2" t="inlineStr">
+      <c r="K92" s="2" t="inlineStr">
         <is>
           <t>R-23 (High)</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>EXT-35</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr">
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>Change records</t>
         </is>
       </c>
-      <c r="M92" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6625,55 +8008,70 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
           <t>Test information</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
           <t>docs/ai/DEVELOPMENT_GUARDRAILS.md (UAT naming convention); docs/security/evidence/access/self_service_masters.txt (synthetic SEC-TEST data); docs/ai/ERP_INTEGRATION.md (dev holds a copy of real ERP data: 18,358 lines, 191 suppliers)</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>TECH PARTIAL: VAPT used synthetic data; dev database also holds real ERP-derived vendor and PO data</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Rule for use of real data in dev; protect dev copies</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr">
         <is>
           <t>Dev lead; ISMS lead</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>Real ERP data on the dev PC</t>
         </is>
       </c>
-      <c r="J93" s="2" t="inlineStr">
+      <c r="K93" s="2" t="inlineStr">
         <is>
           <t>R-25 (Medium)</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>EXT-10</t>
         </is>
       </c>
-      <c r="L93" s="2" t="inlineStr">
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Data inventory of dev</t>
         </is>
       </c>
-      <c r="M93" s="2" t="inlineStr">
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 04</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6692,62 +8090,77 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>PROCESS</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
           <t>Protection of information systems during audit testing</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>docs/security/evidence/infra/static_route_traversal_and_startup.txt (tests on throw-away containers; production not touched); docs/security/evidence/infra/db_03_append_only_privilege_tests.out.txt (all in a rolled-back transaction)</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
+          <t>docs/security/evidence/infra/static_route_traversal_and_startup.txt (tests on throw-away containers; production not touched); docs/security/evidence/infra/db_03_append_only_privilege_tests.out.txt (all in a rolled-back transaction); Closure tests ran only on throw-away stacks (ckam-sec, disposable role-split DB) and a native Windows run with FAKE canary secrets on the dev PC; production and 10.x hosts never touched</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
           <t>TECH READY: VAPT ran on dev/throw-away environments; destructive DB tests rolled back</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Plan approval for any future test touching production</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>CKAM owner</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="J94" s="2" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J94" s="2" t="inlineStr">
+      <c r="K94" s="2" t="inlineStr">
         <is>
           <t>None (supporting control)</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>Keep the rule for the external VAPT (EXT-14)</t>
         </is>
       </c>
-      <c r="L94" s="2" t="inlineStr">
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>Test plan approval</t>
         </is>
       </c>
-      <c r="M94" s="2" t="inlineStr">
+      <c r="N94" s="2" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>DRAFT 13</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>READY</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M94"/>
+  <autoFilter ref="A1:P94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>